--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487627_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487627_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8695</v>
+        <v>7.261</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2099</v>
+        <v>5.7104</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6596</v>
+        <v>1.5506</v>
       </c>
       <c r="G2" t="n">
         <v>0.0207</v>
@@ -610,13 +610,13 @@
         <v>3.1045</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1034</v>
+        <v>-0.7119</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9074</v>
+        <v>-0.4069</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.196</v>
+        <v>-0.305</v>
       </c>
       <c r="V2" t="n">
         <v>4.8477</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4046</v>
+        <v>6.2861</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6989</v>
+        <v>5.4987</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7057</v>
+        <v>0.7875</v>
       </c>
       <c r="G3" t="n">
         <v>4.2919</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2485</v>
+        <v>0.1301</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1222</v>
+        <v>-0.078</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1263</v>
+        <v>0.2081</v>
       </c>
       <c r="V3" t="n">
         <v>0.894</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>D. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2363</v>
+        <v>2.6462</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5006</v>
+        <v>0.1274</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7357</v>
+        <v>2.5188</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7525</v>
+        <v>0.895</v>
       </c>
       <c r="H4" t="n">
-        <v>0.627</v>
+        <v>1.3882</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1256</v>
+        <v>-0.4933</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0644</v>
+        <v>0.0447</v>
       </c>
       <c r="K4" t="n">
-        <v>1.001</v>
+        <v>1.3388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0634</v>
+        <v>-1.2941</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6881</v>
+        <v>0.8502</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.374</v>
+        <v>0.0494</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0622</v>
+        <v>0.8008</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6494</v>
+        <v>0.1214</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1541</v>
+        <v>0.0827</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4953</v>
+        <v>0.0387</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9418</v>
+        <v>0.6597</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ALMENARA SANABRIAS</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6646</v>
+        <v>1.9082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2275</v>
+        <v>1.4996</v>
       </c>
       <c r="F5" t="n">
-        <v>2.437</v>
+        <v>0.4086</v>
       </c>
       <c r="G5" t="n">
-        <v>0.895</v>
+        <v>1.7525</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3882</v>
+        <v>0.627</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4933</v>
+        <v>1.1256</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0447</v>
+        <v>1.0644</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3388</v>
+        <v>1.001</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2941</v>
+        <v>0.0634</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8502</v>
+        <v>0.6881</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0494</v>
+        <v>-0.374</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8008</v>
+        <v>1.0622</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1397</v>
+        <v>0.3213</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1828</v>
+        <v>0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0431</v>
+        <v>0.1683</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6597</v>
+        <v>-0.9418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6597</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6512</v>
+        <v>0.3494</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0699</v>
+        <v>-1.6724</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7211</v>
+        <v>2.0218</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.0087</v>
+        <v>-1.4465</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.2485</v>
+        <v>-2.1478</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7602</v>
+        <v>0.7013</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.9016</v>
+        <v>-1.3833</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.6075</v>
+        <v>-1.2893</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2941</v>
+        <v>-0.0939</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1071</v>
+        <v>-0.0633</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.641</v>
+        <v>-0.8585</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5339</v>
+        <v>0.7952</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>2.5224</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9524</v>
+        <v>-1.0086</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6079</v>
+        <v>-0.5712</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3446</v>
+        <v>-0.4374</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5433</v>
+        <v>0.2821</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5694</v>
+        <v>0.2414</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3731</v>
+        <v>-1.2791</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8037</v>
+        <v>1.5205</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4465</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1478</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7013</v>
+        <v>0.0172</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3833</v>
+        <v>-1.2377</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2893</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0939</v>
+        <v>-0.6445</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0633</v>
+        <v>0.3602</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8585</v>
+        <v>-0.3015</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7952</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5224</v>
+        <v>0.7761</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5224</v>
+        <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9273</v>
+        <v>-0.5513</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2719</v>
+        <v>-0.2473</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6554</v>
+        <v>-0.3039</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>1.1761</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5772</v>
+        <v>-0.1947</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8797</v>
+        <v>-2.6704</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3024</v>
+        <v>2.4758</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-4.0087</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-3.2485</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0172</v>
+        <v>-0.7602</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2377</v>
+        <v>-3.9016</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-2.6075</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6445</v>
+        <v>-1.2941</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3602</v>
+        <v>-0.1071</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3015</v>
+        <v>-0.641</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.5339</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3699</v>
+        <v>0.1065</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8479</v>
+        <v>0.0073</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.522</v>
+        <v>0.0993</v>
       </c>
       <c r="V9" t="n">
-        <v>0.894</v>
+        <v>2.5433</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1761</v>
+        <v>1.2239</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>1.3194</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7834</v>
+        <v>-1.4375</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.574</v>
+        <v>-2.1736</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7906</v>
+        <v>0.7361</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1915</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8248</v>
+        <v>-0.4789</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0296</v>
+        <v>-0.6292</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2048</v>
+        <v>0.1503</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3194</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0381</v>
+        <v>-2.4102</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7799</v>
+        <v>-2.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7418</v>
+        <v>-0.1102</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1161</v>
+        <v>-2.4593</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5866</v>
+        <v>-2.4593</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4705</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2648</v>
+        <v>-1.9402</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.346</v>
+        <v>-1.2729</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.6673</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1487</v>
+        <v>-0.5191</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2406</v>
+        <v>-1.1864</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3893</v>
+        <v>0.6673</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5224</v>
+        <v>0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1646</v>
+        <v>-0.533</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3656</v>
+        <v>-0.3598</v>
       </c>
       <c r="U11" t="n">
-        <v>0.799</v>
+        <v>-0.1733</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2462</v>
+        <v>-2.9568</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9997</v>
+        <v>-4.4806</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2465</v>
+        <v>1.5237</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4593</v>
+        <v>-0.1161</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4593</v>
+        <v>-0.5866</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.4705</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9402</v>
+        <v>-0.2648</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2729</v>
+        <v>-0.346</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6673</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5191</v>
+        <v>0.1487</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1864</v>
+        <v>-0.2406</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6673</v>
+        <v>0.3893</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5821</v>
+        <v>-2.5224</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.369</v>
+        <v>0.2459</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0595</v>
+        <v>-0.3351</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3095</v>
+        <v>0.581</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3895</v>
+        <v>-5.4708</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.6487</v>
+        <v>-7.948</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2592</v>
+        <v>2.4772</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9765</v>
@@ -1468,13 +1468,13 @@
         <v>2.3284</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8309</v>
+        <v>-0.9121</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.5142</v>
+        <v>-0.8135</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3167</v>
+        <v>-0.0987</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.570499999999999</v>
+        <v>6.570400000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.728100000000001</v>
+        <v>-9.728</v>
       </c>
       <c r="F14" t="n">
-        <v>16.2984</v>
+        <v>16.2985</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.0954</v>
+        <v>-7.095400000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-9.820400000000001</v>
@@ -1534,10 +1534,10 @@
         <v>-7.192600000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>8.591900000000001</v>
+        <v>8.591899999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>9.701699999999999</v>
+        <v>9.701700000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-7.761299999999999</v>
@@ -1546,13 +1546,13 @@
         <v>17.463</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.3313</v>
+        <v>-3.3312</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.258500000000001</v>
+        <v>-3.2585</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07269999999999988</v>
+        <v>-0.0726000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>7.295400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2474</v>
+        <v>2.6111</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9069</v>
+        <v>-1.1071</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1543</v>
+        <v>3.7182</v>
       </c>
       <c r="G15" t="n">
         <v>3.685</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3087</v>
+        <v>0.6724</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.12</v>
+        <v>-0.3202</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4287</v>
+        <v>0.9926</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1652</v>
+        <v>2.3182</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1094</v>
+        <v>2.8775</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2746</v>
+        <v>-0.5592</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5256</v>
+        <v>1.8171</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0663</v>
+        <v>1.0686</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4593</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4653</v>
+        <v>1.674</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3841</v>
+        <v>1.0422</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.6318</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0603</v>
+        <v>0.1431</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6821</v>
+        <v>0.0263</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3781</v>
+        <v>0.1168</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.7761</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2963</v>
+        <v>-0.1063</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3656</v>
+        <v>-0.2263</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9307</v>
+        <v>0.12</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6866</v>
+        <v>1.3836</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6866</v>
+        <v>-1.0164</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7087</v>
+        <v>1.629</v>
       </c>
       <c r="E17" t="n">
-        <v>2.377</v>
+        <v>-0.2095</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6683</v>
+        <v>1.8385</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8171</v>
+        <v>2.5256</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0686</v>
+        <v>2.0663</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.4593</v>
       </c>
       <c r="J17" t="n">
-        <v>1.674</v>
+        <v>1.4653</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0422</v>
+        <v>1.3841</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6318</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1431</v>
+        <v>1.0603</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0263</v>
+        <v>0.6821</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1168</v>
+        <v>0.3781</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7158</v>
+        <v>0.7602</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7268</v>
+        <v>0.2655</v>
       </c>
       <c r="U17" t="n">
-        <v>0.011</v>
+        <v>0.4947</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3836</v>
+        <v>-0.6866</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0164</v>
+        <v>-0.6866</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2826</v>
+        <v>0.4283</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1784</v>
+        <v>0.0218</v>
       </c>
       <c r="F18" t="n">
-        <v>0.461</v>
+        <v>0.4065</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0065</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5817</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2434</v>
+        <v>0.4436</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3383</v>
+        <v>0.2838</v>
       </c>
       <c r="V18" t="n">
         <v>0.7075</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3607</v>
+        <v>0.0314</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1997</v>
+        <v>-1.978</v>
       </c>
       <c r="F19" t="n">
-        <v>2.839</v>
+        <v>2.0094</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4885</v>
+        <v>2.5849</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3256</v>
+        <v>4.2149</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1629</v>
+        <v>-1.63</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5402</v>
+        <v>1.1187</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7538</v>
+        <v>3.6662</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2941</v>
+        <v>-2.5475</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0287</v>
+        <v>1.4662</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5718</v>
+        <v>0.5487</v>
       </c>
       <c r="O19" t="n">
-        <v>1.457</v>
+        <v>0.9176</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5821</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5209</v>
+        <v>0.5271</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0595</v>
+        <v>0.2198</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5803</v>
+        <v>0.3073</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.788</v>
+        <v>-0.1702</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>0.5642</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1283</v>
+        <v>-0.7343</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5638</v>
+        <v>-0.2546</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6249</v>
+        <v>-0.4247</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0611</v>
+        <v>0.1702</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4424</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1214</v>
+        <v>0.1879</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0606</v>
+        <v>0.1396</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.5064</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3784</v>
+        <v>-3.3999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6278</v>
+        <v>2.8935</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5849</v>
+        <v>1.4885</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2149</v>
+        <v>1.3256</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.63</v>
+        <v>0.1629</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1187</v>
+        <v>-0.5402</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6662</v>
+        <v>0.7538</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.5475</v>
+        <v>-1.2941</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4662</v>
+        <v>2.0287</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5487</v>
+        <v>0.5718</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9176</v>
+        <v>1.457</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9105</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2548</v>
+        <v>0.3752</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1806</v>
+        <v>-0.2597</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0742</v>
+        <v>0.6348</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1702</v>
+        <v>-1.788</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7343</v>
+        <v>-1.1283</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9017</v>
+        <v>-2.5196</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9074</v>
+        <v>-2.6071</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0057</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7952</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7945</v>
+        <v>-0.4125</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7874</v>
+        <v>-0.4871</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0072</v>
+        <v>0.0746</v>
       </c>
       <c r="V22" t="n">
         <v>-1.506</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3783</v>
+        <v>-4.0423</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4835</v>
+        <v>-4.984</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1052</v>
+        <v>0.9417</v>
       </c>
       <c r="G23" t="n">
         <v>0.7495000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8365</v>
+        <v>0.1724</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3656</v>
+        <v>-0.1349</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4709</v>
+        <v>0.3073</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0537</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0193</v>
+        <v>-6.2656</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8868</v>
+        <v>-4.4874</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1325</v>
+        <v>-1.7782</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5109</v>
@@ -2326,13 +2326,13 @@
         <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6736</v>
+        <v>0.4273</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0329</v>
+        <v>0.4323</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3593</v>
+        <v>-0.005</v>
       </c>
       <c r="V24" t="n">
         <v>-3.1821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.570400000000001</v>
+        <v>-6.570500000000001</v>
       </c>
       <c r="E25" t="n">
         <v>-16.2984</v>
       </c>
       <c r="F25" t="n">
-        <v>9.7279</v>
+        <v>9.7281</v>
       </c>
       <c r="G25" t="n">
         <v>7.095599999999999</v>
@@ -2404,13 +2404,13 @@
         <v>7.7614</v>
       </c>
       <c r="S25" t="n">
-        <v>3.331199999999999</v>
+        <v>3.331</v>
       </c>
       <c r="T25" t="n">
-        <v>0.07259999999999978</v>
+        <v>0.07260000000000022</v>
       </c>
       <c r="U25" t="n">
-        <v>3.2584</v>
+        <v>3.258300000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-7.295500000000001</v>
